--- a/dados/dicionarios/dicionarios.xlsx
+++ b/dados/dicionarios/dicionarios.xlsx
@@ -10,13 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FF106B-834A-4791-B1D2-830449B728EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="censo_bronze" sheetId="1" r:id="rId1"/>
-    <sheet name="censo_silver" sheetId="2" r:id="rId2"/>
-    <sheet name="pns_bronze" sheetId="3" r:id="rId3"/>
-    <sheet name="pns_silver" sheetId="4" r:id="rId4"/>
+    <sheet name="bronze" sheetId="1" r:id="rId1"/>
+    <sheet name="silver" sheetId="2" r:id="rId2"/>
+    <sheet name="sistema" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -589,353 +588,2217 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="83.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="3"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tabela censo_bronze</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Identificador da categoria etária usado pelo IBGE para distinguir cada faixa ou totalização.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Codigo_idade</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Faixa ou categoria etária associada ao total populacional, como idade em anos ou grupo de idades.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Idade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Número de habitantes contabilizados na categoria etária para o município em 2022.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Populacao_2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Código geográfico de sete dígitos que identifica o município na divisão territorial do IBGE.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Codigo_municipio</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Nome do município ao qual pertencem as contagens populacionais.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Tabela pns_bronze</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Código numérico da unidade da federação onde a entrevista foi realizada.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>V0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Identificador do estrato amostral ao qual a observação da pesquisa pertence.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>V0024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Identificador da unidade primária de amostragem (UPA) da entrevista.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>UPA_PNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Idade declarada pelo participante, em anos.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>C008</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Resposta do participante à pergunta da PNS sobre dor crônica.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Q084</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Peso amostral associado ao participante, usado para representar a população no desenho da pesquisa.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>V00291</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C6" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="78.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="83" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="65" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="90" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>24</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tabela censo_silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>regra_campo</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Uma linha por faixa etária detalhada, rótulos em minúsculas, sem acentos e com sublinhados.</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Grupo etário detalhado usado para organizar a população, expresso em meses ou anos completos.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>faixa_etaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Número inteiro maior ou igual a zero.</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Quantidade de habitantes do município que pertence à faixa etária indicada.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>qtd_amostra</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Usar a sigla da cidade, hífen e sigla do estado. Neste conjunto, SCS-SP.</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Município ao qual todas as contagens da tabela se referem: São Caetano do Sul, SP.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Tabela pns_silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>regra_campo</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Deve conter uma sigla válida de UF brasileira.</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Sigla da unidade da federação onde foi realizada a entrevista.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>uf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Código obrigatório, preservado como texto.</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>STRING</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Código da Unidade Primária de Amostragem (UPA) da PNS, unidade do desenho amostral identificada nos microdados, não se refere a uma Unidade de Pronto Atendimento.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>codigo_upa</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Número inteiro maior ou igual a zero, zeros à esquerda são removidos.</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Idade do participante em anos, conforme registrada na pesquisa.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>idade</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Aceita somente 1 (sim) ou 0 (não), respostas sem valor são excluídas.</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Indica se o participante respondeu afirmativamente à pergunta sobre dor crônica.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>dor_cronica</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Número inteiro não negativo, arredondado para o inteiro mais próximo.</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Peso amostral do participante após arredondamento, que permite ponderar sua representação na população.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>peso_amostral_pns</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D4" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C148"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="86.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>37</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tabela cargo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico do registro.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(45)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Nome do cargo do funcionario.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Descricao do cargo ou item.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>descricao</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Tabela endereco</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico do registro.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(9)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Codigo postal do endereco.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>cep</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(120)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Rua, avenida ou via do endereco.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>logradouro</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(80)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Bairro do endereco.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>bairro</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(80)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Cidade do endereco.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>cidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(2)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Sigla da unidade federativa.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>uf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Numero do endereco.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>numero</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(60)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Complemento do endereco, quando informado.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>complemento</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Tabela usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico do registro.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(120)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Nome do registro.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Telefone de contato do usuario.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>telefone</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(120)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Endereco de e-mail do usuario.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Hash da senha de autenticacao.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>senha</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Data de nascimento do usuario.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>data_nascimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TINYINT(1)</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Indica se o usuario esta ativo (1=sim, 0=nao).</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>ativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela endereco.</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>fkEndereco</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Tabela funcionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico do registro.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela usuario.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>fkUsuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela cargo.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>fkCargo</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Tabela agenda_excecao</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico do registro.</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela funcionario.</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>fkFuncionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Data da excecao na agenda.</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Horario de inicio da disponibilidade ou excecao.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>hora_inicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Horario de termino da disponibilidade ou excecao.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>hora_fim</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>TINYINT(1)</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Indica se o funcionario esta disponivel no periodo (1=sim, 0=nao).</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>disponivel</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Tabela agenda_funcionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico do registro.</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela funcionario.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>fkFuncionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Dia da semana (MySQL DAYOFWEEK: 1=domingo a 7=sabado).</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>dia_semana</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Horario de inicio da disponibilidade ou excecao.</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>hora_inicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Horario de termino da disponibilidade ou excecao.</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>hora_fim</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>Tabela cliente</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico do registro.</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela usuario.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>fkUsuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Observacoes adicionais relacionadas ao registro.</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>observacao</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>Tabela sala</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico do registro.</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Descricao do cargo ou item.</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>descricao</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>Tabela status</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico do registro.</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(45)</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Nome do status do agendamento.</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Tabela agendamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico do registro.</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Data e hora de inicio do agendamento.</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>data_hora_inicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Data e hora de termino do agendamento.</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>data_hora_fim</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Observacoes adicionais relacionadas ao registro.</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>observacao</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela cliente.</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>fkCliente</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela sala.</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>fkSala</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela status.</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>fkStatus</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>Tabela funcionario_agendamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela funcionario.</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>fkFuncionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela agendamento.</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>fkAgendamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>Tabela servico</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico do registro.</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Nome do servico oferecido.</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>DECIMAL(10,2)</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Preco atual do servico.</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Descricao do cargo ou item.</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>descricao</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Duracao media estimada do servico, em minutos.</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>tempoMedio</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>Tabela atendimento_servico</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico do registro.</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>DECIMAL(10,2)</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Valor cobrado pelo servico neste atendimento.</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>valor_unitario</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela servico.</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>fkServico</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela agendamento.</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>fkAgendamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Descricao do servico realizado no atendimento.</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>descricao</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Observacoes adicionais do atendimento.</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>observacoes</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>Tabela especialidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico do registro.</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(60)</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Nome da especialidade oferecida.</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>Tabela especialidade_servico</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela especialidade.</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>fkEspecialidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela servico.</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>fkServico</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>Tabela funcionario_especialidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela funcionario.</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>fkFuncionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela especialidade.</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>fkEspecialidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>Tabela permissoes</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico do registro.</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(45)</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Nome do registro.</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Descricao do cargo ou item.</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>descricao</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>Tabela permissoes_cargo</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B139" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela permissoes.</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>fkPermissoes</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela cargo.</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>fkCargo</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>Tabela sala_servico</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B145" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela sala.</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>fkSala</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a tabela servico.</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>fkServico</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C7" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="60.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="144" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D6" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dados/dicionarios/dicionarios.xlsx
+++ b/dados/dicionarios/dicionarios.xlsx
@@ -1092,9 +1092,1273 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C165"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2799,6 +4063,224 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>Tabela triagem_pergunta</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B151" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico da pergunta de triagem.</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(500)</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Texto apresentado como pergunta durante a triagem.</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Ordem de exibicao da pergunta.</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>ordem</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>TINYINT(1)</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Indica se a pergunta e uma pergunta raiz (1=sim, 0=nao).</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>raiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira opcional que referencia a tabela especialidade.</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>fk_especialidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>Tabela triagem_resposta</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B160" s="1" t="inlineStr">
+        <is>
+          <t>descricao_campo</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Identificador unico da resposta de triagem.</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira que referencia a pergunta de triagem.</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>fk_pergunta</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>ENUM('SIM','NAO')</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Resposta possivel para a pergunta de triagem.</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>resposta</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira opcional que referencia a proxima pergunta.</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>fk_proxima_pergunta</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Chave estrangeira opcional que referencia a tabela especialidade.</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>fk_especialidade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>